--- a/手順-all.xlsx
+++ b/手順-all.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17010" tabRatio="911" firstSheet="1" activeTab="1"/>
+    <workbookView windowHeight="17010" tabRatio="911" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="331" r:id="rId1"/>
